--- a/data/availability/projects/m-squared-developments/business-district.xlsx
+++ b/data/availability/projects/m-squared-developments/business-district.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -575,7 +575,6 @@
       <c r="H2" t="n">
         <v>21.68</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>41 business district</t>
@@ -583,7 +582,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -681,7 +680,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -697,11 +696,9 @@
       <c r="E2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>195</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -712,7 +709,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -734,7 +731,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -750,11 +747,9 @@
       <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>220</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -765,7 +760,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -787,7 +782,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -803,11 +798,9 @@
       <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>220</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -818,7 +811,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -840,7 +833,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -856,11 +849,9 @@
       <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>180</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -871,7 +862,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -893,7 +884,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -909,11 +900,9 @@
       <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>150</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -924,7 +913,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -946,7 +935,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -962,11 +951,9 @@
       <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>185</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -977,7 +964,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -999,7 +986,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1015,11 +1002,9 @@
       <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>145</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1030,7 +1015,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1052,7 +1037,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,11 +1053,9 @@
       <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>130</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1083,7 +1066,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1105,7 +1088,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1121,11 +1104,9 @@
       <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>130</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1136,7 +1117,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1158,7 +1139,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1174,11 +1155,9 @@
       <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>210</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1189,7 +1168,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2/5/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
